--- a/AAII_Financials/Quarterly/URMCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/URMCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>URMCY</t>
   </si>
@@ -655,68 +655,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -750,8 +758,14 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,8 +799,14 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,8 +840,14 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,8 +861,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,8 +898,14 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +939,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,8 +980,14 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -975,8 +1021,14 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,8 +1039,10 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1022,8 +1076,14 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1057,8 +1117,14 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,8 +1138,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1107,8 +1175,14 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1142,8 +1216,14 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1177,8 +1257,14 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1212,8 +1298,14 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1247,8 +1339,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,8 +1380,14 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1317,8 +1421,14 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1352,8 +1462,14 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1503,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1544,14 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1585,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,8 +1626,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1527,8 +1667,14 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1562,8 +1708,14 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,8 +1749,14 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1632,48 +1790,60 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1857,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,43 +1874,51 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3239700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3269600</v>
+      </c>
+      <c r="F41" s="3">
         <v>3147200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3145000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3883900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3574500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5475600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5898800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4950400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4984600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6081900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5823800</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,253 +1952,301 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1446100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1459500</v>
+      </c>
+      <c r="F43" s="3">
         <v>1386100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1385100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1673400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1540100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1126800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1213900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1417800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1427600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1342500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1285600</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>33400</v>
+      </c>
+      <c r="F44" s="3">
         <v>24900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>24900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>28900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>26600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>18200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>19600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>35000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>35300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>39000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>174600</v>
+      </c>
+      <c r="F45" s="3">
         <v>107900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>107800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>365400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>336300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>752900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>811100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>638400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>642800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>226000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>216400</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4891900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4937000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4666100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4662800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5951500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5477400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7373500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7943500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7041600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7090200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7689500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>7363100</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8478900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>8557100</v>
+      </c>
+      <c r="F47" s="3">
         <v>8366800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>8360900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>8253600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>7596100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>7545900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>8129200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>7585600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>7637900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>8003000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>7663300</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>42333800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>42724300</v>
+      </c>
+      <c r="F48" s="3">
         <v>43428100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>43397500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>43556900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>40087200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>38540200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>41519100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>40074800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>40351500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>41374200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>39618100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1590900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1605600</v>
+      </c>
+      <c r="F49" s="3">
         <v>1628200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1627000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1847000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1699800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1704300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1836000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1783600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1795900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1851200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1772700</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2280,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,43 +2321,55 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>261300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>263700</v>
+      </c>
+      <c r="F52" s="3">
         <v>229300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>229100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>165700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>152500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>259400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>279500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>539900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>543600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>277100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>265300</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,43 +2403,55 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>57581400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>58112500</v>
+      </c>
+      <c r="F54" s="3">
         <v>58335100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>58294000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>59795000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>55031800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>55436000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>59720700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>57052500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>57446400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>59222000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>56708400</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2465,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,218 +2482,256 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>376800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>380300</v>
+      </c>
+      <c r="F57" s="3">
         <v>349400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>349200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>381300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>351000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>248600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>267800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>246100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>247800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>270800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3934500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3970800</v>
+      </c>
+      <c r="F58" s="3">
         <v>1312400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1311500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3805600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3502500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3362000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3621900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3684600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3710000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2090700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2002000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1907600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1925200</v>
+      </c>
+      <c r="F59" s="3">
         <v>2012100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2010700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2215500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2039000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1746800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1881800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1808200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1820700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1879700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1800000</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6218900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6276300</v>
+      </c>
+      <c r="F60" s="3">
         <v>3673900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3671400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6402500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5892500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5357400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5771500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5738900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5778500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4241300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4061300</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23230200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>23444500</v>
+      </c>
+      <c r="F61" s="3">
         <v>26264300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>26245800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>26174200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>24089200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>25959400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>27965900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>26893600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>27079300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>29623000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>28365700</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>453900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>458100</v>
+      </c>
+      <c r="F62" s="3">
         <v>468900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>468600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>420100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>386600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>393200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>423600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>414200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>417100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>420000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>402200</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2765,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2806,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,43 +2847,55 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32452600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>32752000</v>
+      </c>
+      <c r="F66" s="3">
         <v>32860300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>32837100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>35304200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>32491900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>33655700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>36257000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>34996900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>35238500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>36267000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>34727800</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2909,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2946,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2987,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +3028,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,43 +3069,55 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1152900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1163500</v>
+      </c>
+      <c r="F72" s="3">
         <v>1489000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1488000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>819400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>754100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>151400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>163100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>76800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>77400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1800700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1724300</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +3151,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3192,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,43 +3233,55 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20440800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20629300</v>
+      </c>
+      <c r="F76" s="3">
         <v>20784700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20770000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>19943200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>18354500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>18294500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19708600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>18279400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18405700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19019300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>18212100</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,48 +3315,60 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3012,8 +3402,14 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,43 +3423,51 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F83" s="3">
         <v>53900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>58100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>8800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>8400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>7300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3501,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3542,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3583,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3624,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3665,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>564300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>569500</v>
+      </c>
+      <c r="F89" s="3">
         <v>650600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>650200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>550900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>507000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>658300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>709200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>492000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>495400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>626500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>599900</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,8 +3727,10 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3322,8 +3764,14 @@
       <c r="M91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3805,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,43 +3846,55 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>166600</v>
+      </c>
+      <c r="F94" s="3">
         <v>36500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>36400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>345600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>318100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>81100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>87300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-371600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-374200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-308900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-295800</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,43 +3908,51 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>380100</v>
+      </c>
+      <c r="F96" s="3">
         <v>17100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>17100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>328700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>302500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>40000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>43100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>198000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>199300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>20500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3986,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +4027,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,109 +4068,133 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-653700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-659700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1067100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1066300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2023500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1862300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-393400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-423800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-601300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-605400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>579900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>555300</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-36600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>9500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>9600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>31800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>30500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-7200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-7200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>6600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>90000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-367000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-366800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1163500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1070800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>344900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>371500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-471300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-474600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>929300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>889900</v>
       </c>
     </row>
